--- a/RiskHalo_Certification_Challenge/data/Weekly_Trade_Data_Uploads/Week_17_Trade_data.xlsx
+++ b/RiskHalo_Certification_Challenge/data/Weekly_Trade_Data_Uploads/Week_17_Trade_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SOFTWARES\CodeRepo\AIE9_CERTIFICATION_CHALLENGE\RiskHalo_Certification_Challenge\data\Weekly_Trade_Data_Uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{812C2F7F-A91C-41F1-A3D3-74E92B7D90A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9BD8EF4-A3CD-4AFE-B168-F835E0CDED3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="44">
   <si>
     <t>Sr.</t>
   </si>
@@ -55,58 +55,91 @@
     <t>Turnover</t>
   </si>
   <si>
-    <t>OPT SUNPHARMA 28 Aug 2025 1620 PE</t>
-  </si>
-  <si>
-    <t>04-08-2025</t>
-  </si>
-  <si>
-    <t>OPT DLF 28 Aug 2025 760 PE</t>
-  </si>
-  <si>
-    <t>05-08-2025</t>
-  </si>
-  <si>
-    <t>OPT COLPAL 28 Aug 2025 2240 CE</t>
-  </si>
-  <si>
-    <t>OPT COALINDIA 28 Aug 2025 375 PE</t>
-  </si>
-  <si>
-    <t>OPT BSE 28 Aug 2025 2400 PE</t>
-  </si>
-  <si>
-    <t>OPT BOSCHLTD 28 Aug 2025 41000 CE</t>
-  </si>
-  <si>
-    <t>OPT AUROPHARMA 28 Aug 2025 1100 PE</t>
-  </si>
-  <si>
-    <t>OPT BEL 28 Aug 2025 400 CE</t>
-  </si>
-  <si>
-    <t>06-08-2025</t>
-  </si>
-  <si>
-    <t>OPT KAYNES 28 Aug 2025 6200 PE</t>
-  </si>
-  <si>
-    <t>OPT APLAPOLLO 28 Aug 2025 1560 PE</t>
-  </si>
-  <si>
-    <t>07-08-2025</t>
-  </si>
-  <si>
-    <t>OPT DIVISLAB 28 Aug 2025 6100 PE</t>
-  </si>
-  <si>
-    <t>OPT DIVISLAB 28 Aug 2025 6000 PE</t>
-  </si>
-  <si>
-    <t>OPT SYNGENE 28 Aug 2025 670 PE</t>
-  </si>
-  <si>
-    <t>OPT ZYDUSLIFE 28 Aug 2025 930 CE</t>
+    <t>OPT EICHERMOT 30 Sep 2025 6600 CE</t>
+  </si>
+  <si>
+    <t>08-09-2025</t>
+  </si>
+  <si>
+    <t>OPT ITC 30 Sep 2025 405 CE</t>
+  </si>
+  <si>
+    <t>OPT ASHOKLEY 30 Sep 2025 135 CE</t>
+  </si>
+  <si>
+    <t>OPT LTIM 30 Sep 2025 5200 CE</t>
+  </si>
+  <si>
+    <t>09-09-2025</t>
+  </si>
+  <si>
+    <t>OPT NIFTY 09 Sep 2025 24800 PE</t>
+  </si>
+  <si>
+    <t>OPT SBIN 30 Sep 2025 810 PE</t>
+  </si>
+  <si>
+    <t>OPT TATAELXSI 30 Sep 2025 5500 CE</t>
+  </si>
+  <si>
+    <t>OPT WIPRO 30 Sep 2025 250 CE</t>
+  </si>
+  <si>
+    <t>OPT NIFTY 09 Sep 2025 25000 CE</t>
+  </si>
+  <si>
+    <t>OPT ADANIPORTS 30 Sep 2025 1360 CE</t>
+  </si>
+  <si>
+    <t>OPT PPLPHARMA 30 Sep 2025 200 CE</t>
+  </si>
+  <si>
+    <t>10-09-2025</t>
+  </si>
+  <si>
+    <t>OPT DRREDDY 30 Sep 2025 1300 CE</t>
+  </si>
+  <si>
+    <t>OPT TVSMOTOR 30 Sep 2025 3550 PE</t>
+  </si>
+  <si>
+    <t>OPT TCS 30 Sep 2025 3100 CE</t>
+  </si>
+  <si>
+    <t>OPT AUROPHARMA 30 Sep 2025 1060 CE</t>
+  </si>
+  <si>
+    <t>OPT ADANIENT 30 Sep 2025 2400 CE</t>
+  </si>
+  <si>
+    <t>11-09-2025</t>
+  </si>
+  <si>
+    <t>OPT DRREDDY 30 Sep 2025 1300 PE</t>
+  </si>
+  <si>
+    <t>OPT NHPC 30 Sep 2025 82 CE</t>
+  </si>
+  <si>
+    <t>OPT BANKINDIA 30 Sep 2025 115 CE</t>
+  </si>
+  <si>
+    <t>OPT EICHERMOT 30 Sep 2025 6850 CE</t>
+  </si>
+  <si>
+    <t>12-09-2025</t>
+  </si>
+  <si>
+    <t>OPT BSE 30 Sep 2025 2200 CE</t>
+  </si>
+  <si>
+    <t>OPT GAIL 30 Sep 2025 180 CE</t>
+  </si>
+  <si>
+    <t>OPT MOTHERSON 30 Sep 2025 100 CE</t>
+  </si>
+  <si>
+    <t>OPT HAL 30 Sep 2025 4600 CE</t>
   </si>
   <si>
     <t>Buy Qty</t>
@@ -459,10 +492,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="34.28515625" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.140625" style="1"/>
   </cols>
@@ -478,10 +511,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E1" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -490,10 +523,10 @@
         <v>4</v>
       </c>
       <c r="H1" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="I1" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="J1" t="s">
         <v>5</v>
@@ -516,660 +549,1130 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>254</v>
+        <v>100</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="1">
-        <v>45873</v>
+        <v>45908</v>
       </c>
       <c r="D2">
-        <v>700</v>
+        <v>175</v>
       </c>
       <c r="E2">
-        <v>36.6</v>
+        <v>134</v>
       </c>
       <c r="F2">
-        <v>25620</v>
+        <v>23450</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H2">
-        <v>700</v>
+        <v>175</v>
       </c>
       <c r="I2">
-        <v>33.799999999999997</v>
+        <v>149</v>
       </c>
       <c r="J2">
-        <v>23660</v>
+        <v>26075</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>-1960</v>
+        <v>2625</v>
       </c>
       <c r="M2">
-        <v>92.92</v>
+        <v>95.3</v>
       </c>
       <c r="N2">
-        <v>-2052.92</v>
+        <v>2529.6999999999998</v>
       </c>
       <c r="O2">
-        <v>1960</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>90</v>
+        <v>137</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="1">
-        <v>45874</v>
+        <v>45908</v>
       </c>
       <c r="D3">
-        <v>825</v>
+        <v>1600</v>
       </c>
       <c r="E3">
-        <v>16.350000000000001</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="F3">
-        <v>13488.75</v>
+        <v>14080</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H3">
-        <v>825</v>
+        <v>1600</v>
       </c>
       <c r="I3">
-        <v>14.55</v>
+        <v>8.35</v>
       </c>
       <c r="J3">
-        <v>12003.75</v>
+        <v>13360</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>-1485</v>
+        <v>-720</v>
       </c>
       <c r="M3">
-        <v>70.319999999999993</v>
+        <v>72.52</v>
       </c>
       <c r="N3">
-        <v>-1555.32</v>
+        <v>-792.52</v>
       </c>
       <c r="O3">
-        <v>1485</v>
+        <v>720</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1">
-        <v>45874</v>
+        <v>45908</v>
       </c>
       <c r="D4">
-        <v>225</v>
+        <v>5000</v>
       </c>
       <c r="E4">
-        <v>53.6</v>
+        <v>4.55</v>
       </c>
       <c r="F4">
-        <v>12060</v>
+        <v>22750</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H4">
-        <v>225</v>
+        <v>5000</v>
       </c>
       <c r="I4">
-        <v>52.3</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="J4">
-        <v>11767.5</v>
+        <v>24250</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>-292.5</v>
+        <v>1500</v>
       </c>
       <c r="M4">
-        <v>69.349999999999994</v>
+        <v>91.89</v>
       </c>
       <c r="N4">
-        <v>-361.85</v>
+        <v>1408.11</v>
       </c>
       <c r="O4">
-        <v>292.5</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>58</v>
+        <v>168</v>
       </c>
       <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="1">
+        <v>45909</v>
+      </c>
+      <c r="D5">
+        <v>150</v>
+      </c>
+      <c r="E5">
+        <v>135</v>
+      </c>
+      <c r="F5">
+        <v>20250</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="1">
-        <v>45874</v>
-      </c>
-      <c r="D5">
-        <v>1350</v>
-      </c>
-      <c r="E5">
-        <v>12.5</v>
-      </c>
-      <c r="F5">
-        <v>16875</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="H5">
-        <v>1350</v>
+        <v>150</v>
       </c>
       <c r="I5">
-        <v>12.15</v>
+        <v>119.05</v>
       </c>
       <c r="J5">
-        <v>16402.5</v>
+        <v>17857.5</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>-472.5</v>
+        <v>-2392.5</v>
       </c>
       <c r="M5">
-        <v>78.099999999999994</v>
+        <v>81.69</v>
       </c>
       <c r="N5">
-        <v>-550.6</v>
+        <v>-2474.19</v>
       </c>
       <c r="O5">
-        <v>472.5</v>
+        <v>2392.5</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>54</v>
+        <v>198</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
       </c>
       <c r="C6" s="1">
-        <v>45874</v>
+        <v>45909</v>
       </c>
       <c r="D6">
-        <v>1125</v>
+        <v>75</v>
       </c>
       <c r="E6">
-        <v>119.03</v>
+        <v>19.850000000000001</v>
       </c>
       <c r="F6">
-        <v>133912.5</v>
+        <v>1488.75</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H6">
-        <v>1125</v>
+        <v>75</v>
       </c>
       <c r="I6">
-        <v>109.32</v>
+        <v>10.050000000000001</v>
       </c>
       <c r="J6">
-        <v>122981.25</v>
+        <v>753.75</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>-10931.25</v>
+        <v>-735</v>
       </c>
       <c r="M6">
-        <v>352.98</v>
+        <v>48.93</v>
       </c>
       <c r="N6">
-        <v>-11284.23</v>
+        <v>-783.93</v>
       </c>
       <c r="O6">
-        <v>10931.25</v>
+        <v>735</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="1">
-        <v>45874</v>
+        <v>45909</v>
       </c>
       <c r="D7">
-        <v>25</v>
+        <v>750</v>
       </c>
       <c r="E7">
-        <v>1195.0999999999999</v>
+        <v>12.6</v>
       </c>
       <c r="F7">
-        <v>29877.5</v>
+        <v>9450</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H7">
-        <v>25</v>
+        <v>750</v>
       </c>
       <c r="I7">
-        <v>1170.05</v>
+        <v>11.65</v>
       </c>
       <c r="J7">
-        <v>29251.25</v>
+        <v>8737.5</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>-626.25</v>
+        <v>-712.5</v>
       </c>
       <c r="M7">
-        <v>102.21</v>
+        <v>63.87</v>
       </c>
       <c r="N7">
-        <v>-728.46</v>
+        <v>-776.37</v>
       </c>
       <c r="O7">
-        <v>626.25</v>
+        <v>712.5</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>27</v>
+        <v>260</v>
       </c>
       <c r="B8" t="s">
         <v>19</v>
       </c>
       <c r="C8" s="1">
-        <v>45874</v>
+        <v>45909</v>
       </c>
       <c r="D8">
-        <v>1100</v>
+        <v>500</v>
       </c>
       <c r="E8">
-        <v>45.85</v>
+        <v>176.45</v>
       </c>
       <c r="F8">
-        <v>50435</v>
+        <v>88225</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H8">
-        <v>1100</v>
+        <v>500</v>
       </c>
       <c r="I8">
-        <v>47.2</v>
+        <v>174.49</v>
       </c>
       <c r="J8">
-        <v>51920</v>
+        <v>87245</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>1485</v>
+        <v>-980</v>
       </c>
       <c r="M8">
-        <v>190.86</v>
+        <v>329.4</v>
       </c>
       <c r="N8">
-        <v>1294.1400000000001</v>
+        <v>-1309.4000000000001</v>
       </c>
       <c r="O8">
-        <v>1485</v>
+        <v>980</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>42</v>
+        <v>288</v>
       </c>
       <c r="B9" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="1">
-        <v>45875</v>
+        <v>45909</v>
       </c>
       <c r="D9">
-        <v>2850</v>
+        <v>3000</v>
       </c>
       <c r="E9">
-        <v>6.55</v>
+        <v>5.45</v>
       </c>
       <c r="F9">
-        <v>18667.5</v>
+        <v>16350</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H9">
-        <v>2850</v>
+        <v>3000</v>
       </c>
       <c r="I9">
         <v>5.5</v>
       </c>
       <c r="J9">
-        <v>15675</v>
+        <v>16500</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>-2992.5</v>
+        <v>150</v>
       </c>
       <c r="M9">
-        <v>77.88</v>
+        <v>78</v>
       </c>
       <c r="N9">
-        <v>-3070.38</v>
+        <v>72</v>
       </c>
       <c r="O9">
-        <v>2992.5</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>154</v>
+        <v>203</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" s="1">
-        <v>45875</v>
+        <v>45909</v>
       </c>
       <c r="D10">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="E10">
-        <v>246.35</v>
+        <v>5.3</v>
       </c>
       <c r="F10">
-        <v>49270</v>
+        <v>397.5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H10">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="I10">
-        <v>262.8</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="J10">
-        <v>52560</v>
+        <v>82.5</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>3290</v>
+        <v>-315</v>
       </c>
       <c r="M10">
-        <v>190.97</v>
+        <v>47.49</v>
       </c>
       <c r="N10">
-        <v>3099.03</v>
+        <v>-362.49</v>
       </c>
       <c r="O10">
-        <v>3290</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" s="1">
-        <v>45876</v>
+        <v>45909</v>
       </c>
       <c r="D11">
-        <v>350</v>
+        <v>475</v>
       </c>
       <c r="E11">
-        <v>37.700000000000003</v>
+        <v>39.9</v>
       </c>
       <c r="F11">
-        <v>13195</v>
+        <v>18952.5</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H11">
-        <v>350</v>
+        <v>475</v>
       </c>
       <c r="I11">
-        <v>34.75</v>
+        <v>35</v>
       </c>
       <c r="J11">
-        <v>12162.5</v>
+        <v>16625</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>-1032.5</v>
+        <v>-2327.5</v>
       </c>
       <c r="M11">
-        <v>70.42</v>
+        <v>79.36</v>
       </c>
       <c r="N11">
-        <v>-1102.92</v>
+        <v>-2406.86</v>
       </c>
       <c r="O11">
-        <v>1032.5</v>
+        <v>2327.5</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>84</v>
+        <v>242</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C12" s="1">
-        <v>45876</v>
+        <v>45910</v>
       </c>
       <c r="D12">
-        <v>100</v>
+        <v>2500</v>
       </c>
       <c r="E12">
-        <v>149.9</v>
+        <v>7</v>
       </c>
       <c r="F12">
-        <v>14990</v>
+        <v>17500</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H12">
-        <v>100</v>
+        <v>2500</v>
       </c>
       <c r="I12">
-        <v>197</v>
+        <v>7.15</v>
       </c>
       <c r="J12">
-        <v>19700</v>
+        <v>17875</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>4710</v>
+        <v>375</v>
       </c>
       <c r="M12">
-        <v>81.93</v>
+        <v>80.48</v>
       </c>
       <c r="N12">
-        <v>4628.07</v>
+        <v>294.52</v>
       </c>
       <c r="O12">
-        <v>4710</v>
+        <v>375</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C13" s="1">
-        <v>45876</v>
+        <v>45910</v>
       </c>
       <c r="D13">
-        <v>400</v>
+        <v>625</v>
       </c>
       <c r="E13">
-        <v>125.09</v>
+        <v>25.15</v>
       </c>
       <c r="F13">
-        <v>50035</v>
+        <v>15718.75</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H13">
-        <v>400</v>
+        <v>625</v>
       </c>
       <c r="I13">
-        <v>105.95</v>
+        <v>26.1</v>
       </c>
       <c r="J13">
-        <v>42380</v>
+        <v>16312.5</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>-7655</v>
+        <v>593.75</v>
       </c>
       <c r="M13">
-        <v>200.86</v>
+        <v>77.45</v>
       </c>
       <c r="N13">
-        <v>-7855.86</v>
+        <v>516.29999999999995</v>
       </c>
       <c r="O13">
-        <v>7655</v>
+        <v>593.75</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>256</v>
+        <v>283</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" s="1">
-        <v>45876</v>
+        <v>45910</v>
       </c>
       <c r="D14">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="E14">
-        <v>18.100000000000001</v>
+        <v>78.95</v>
       </c>
       <c r="F14">
-        <v>18100</v>
+        <v>27632.5</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H14">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="I14">
-        <v>18.3</v>
+        <v>83</v>
       </c>
       <c r="J14">
-        <v>18300</v>
+        <v>29050</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>200</v>
+        <v>1417.5</v>
       </c>
       <c r="M14">
-        <v>81.34</v>
+        <v>100.85</v>
       </c>
       <c r="N14">
-        <v>118.66</v>
+        <v>1316.65</v>
       </c>
       <c r="O14">
-        <v>200</v>
+        <v>1417.5</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" s="1">
-        <v>45876</v>
+        <v>45910</v>
       </c>
       <c r="D15">
-        <v>900</v>
+        <v>175</v>
       </c>
       <c r="E15">
-        <v>33.5</v>
+        <v>65.849999999999994</v>
       </c>
       <c r="F15">
-        <v>30150</v>
+        <v>11523.75</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H15">
-        <v>900</v>
+        <v>175</v>
       </c>
       <c r="I15">
-        <v>29.5</v>
+        <v>68.900000000000006</v>
       </c>
       <c r="J15">
-        <v>26550</v>
+        <v>12057.5</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>-3600</v>
+        <v>533.75</v>
       </c>
       <c r="M15">
-        <v>98.49</v>
+        <v>69.52</v>
       </c>
       <c r="N15">
-        <v>-3698.49</v>
+        <v>464.23</v>
       </c>
       <c r="O15">
-        <v>3600</v>
+        <v>533.75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="1">
+        <v>45910</v>
+      </c>
+      <c r="D16">
+        <v>550</v>
+      </c>
+      <c r="E16">
+        <v>32.15</v>
+      </c>
+      <c r="F16">
+        <v>17682.5</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H16">
+        <v>550</v>
+      </c>
+      <c r="I16">
+        <v>31</v>
+      </c>
+      <c r="J16">
+        <v>17050</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>-632.5</v>
+      </c>
+      <c r="M16">
+        <v>79.38</v>
+      </c>
+      <c r="N16">
+        <v>-711.88</v>
+      </c>
+      <c r="O16">
+        <v>632.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="1">
+        <v>45911</v>
+      </c>
+      <c r="D17">
+        <v>300</v>
+      </c>
+      <c r="E17">
+        <v>62.3</v>
+      </c>
+      <c r="F17">
+        <v>18690</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H17">
+        <v>300</v>
+      </c>
+      <c r="I17">
+        <v>68</v>
+      </c>
+      <c r="J17">
+        <v>20400</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>1710</v>
+      </c>
+      <c r="M17">
+        <v>84.59</v>
+      </c>
+      <c r="N17">
+        <v>1625.41</v>
+      </c>
+      <c r="O17">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>97</v>
+      </c>
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="1">
+        <v>45911</v>
+      </c>
+      <c r="D18">
+        <v>625</v>
+      </c>
+      <c r="E18">
+        <v>34.75</v>
+      </c>
+      <c r="F18">
+        <v>21718.75</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H18">
+        <v>625</v>
+      </c>
+      <c r="I18">
+        <v>32.25</v>
+      </c>
+      <c r="J18">
+        <v>20156.25</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>-1562.5</v>
+      </c>
+      <c r="M18">
+        <v>85.62</v>
+      </c>
+      <c r="N18">
+        <v>-1648.12</v>
+      </c>
+      <c r="O18">
+        <v>1562.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>183</v>
+      </c>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="1">
+        <v>45911</v>
+      </c>
+      <c r="D19">
+        <v>6400</v>
+      </c>
+      <c r="E19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F19">
+        <v>14080</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H19">
+        <v>6400</v>
+      </c>
+      <c r="I19">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="J19">
+        <v>14720</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>640</v>
+      </c>
+      <c r="M19">
+        <v>74.45</v>
+      </c>
+      <c r="N19">
+        <v>565.54999999999995</v>
+      </c>
+      <c r="O19">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>39</v>
+      </c>
+      <c r="B20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="1">
+        <v>45911</v>
+      </c>
+      <c r="D20">
+        <v>15600</v>
+      </c>
+      <c r="E20">
+        <v>6.22</v>
+      </c>
+      <c r="F20">
+        <v>96980</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H20">
+        <v>15600</v>
+      </c>
+      <c r="I20">
+        <v>6.42</v>
+      </c>
+      <c r="J20">
+        <v>100100</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>3120</v>
+      </c>
+      <c r="M20">
+        <v>327.55</v>
+      </c>
+      <c r="N20">
+        <v>2792.45</v>
+      </c>
+      <c r="O20">
+        <v>3120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>102</v>
+      </c>
+      <c r="B21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="1">
+        <v>45912</v>
+      </c>
+      <c r="D21">
+        <v>175</v>
+      </c>
+      <c r="E21">
+        <v>149.94999999999999</v>
+      </c>
+      <c r="F21">
+        <v>26241.25</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H21">
+        <v>175</v>
+      </c>
+      <c r="I21">
+        <v>148.4</v>
+      </c>
+      <c r="J21">
+        <v>25970</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>-271.25</v>
+      </c>
+      <c r="M21">
+        <v>95.91</v>
+      </c>
+      <c r="N21">
+        <v>-367.16</v>
+      </c>
+      <c r="O21">
+        <v>271.25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>53</v>
+      </c>
+      <c r="B22" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="1">
+        <v>45912</v>
+      </c>
+      <c r="D22">
+        <v>375</v>
+      </c>
+      <c r="E22">
+        <v>109.95</v>
+      </c>
+      <c r="F22">
+        <v>41231.25</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H22">
+        <v>375</v>
+      </c>
+      <c r="I22">
+        <v>103.7</v>
+      </c>
+      <c r="J22">
+        <v>38887.5</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>-2343.75</v>
+      </c>
+      <c r="M22">
+        <v>121.01</v>
+      </c>
+      <c r="N22">
+        <v>-2464.7600000000002</v>
+      </c>
+      <c r="O22">
+        <v>2343.75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>104</v>
+      </c>
+      <c r="B23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="1">
+        <v>45912</v>
+      </c>
+      <c r="D23">
+        <v>3150</v>
+      </c>
+      <c r="E23">
+        <v>6.1</v>
+      </c>
+      <c r="F23">
+        <v>19215</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H23">
+        <v>3150</v>
+      </c>
+      <c r="I23">
+        <v>5.65</v>
+      </c>
+      <c r="J23">
+        <v>17797.5</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>-1417.5</v>
+      </c>
+      <c r="M23">
+        <v>81.14</v>
+      </c>
+      <c r="N23">
+        <v>-1498.64</v>
+      </c>
+      <c r="O23">
+        <v>1417.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>176</v>
+      </c>
+      <c r="B24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="1">
+        <v>45912</v>
+      </c>
+      <c r="D24">
+        <v>18450</v>
+      </c>
+      <c r="E24">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="F24">
+        <v>87330</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H24">
+        <v>18450</v>
+      </c>
+      <c r="I24">
+        <v>4.7</v>
+      </c>
+      <c r="J24">
+        <v>86715</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>-615</v>
+      </c>
+      <c r="M24">
+        <v>304.11</v>
+      </c>
+      <c r="N24">
+        <v>-919.11</v>
+      </c>
+      <c r="O24">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>111</v>
+      </c>
+      <c r="B25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="1">
+        <v>45912</v>
+      </c>
+      <c r="D25">
+        <v>300</v>
+      </c>
+      <c r="E25">
+        <v>171.35</v>
+      </c>
+      <c r="F25">
+        <v>51405</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H25">
+        <v>300</v>
+      </c>
+      <c r="I25">
+        <v>166.65</v>
+      </c>
+      <c r="J25">
+        <v>49995</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>-1410</v>
+      </c>
+      <c r="M25">
+        <v>141.21</v>
+      </c>
+      <c r="N25">
+        <v>-1551.21</v>
+      </c>
+      <c r="O25">
+        <v>1410</v>
       </c>
     </row>
   </sheetData>
